--- a/contents/files/4_實務範例_員工資料輸入表.xlsx
+++ b/contents/files/4_實務範例_員工資料輸入表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shelf\Lecture\114.2 電腦軟體應用\Hello Excel\contents\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0716C4A3-63D0-4B6A-A3D7-B613E9126F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF817D9B-A467-4FB0-A3E1-D877C3BCA011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="員工資料輸入" sheetId="1" r:id="rId1"/>
@@ -84,21 +84,25 @@
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -178,10 +182,10 @@
     <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -495,14 +499,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -583,34 +587,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="年資錯誤" error="年資必須為 0 到 50 之間的整數" promptTitle="輸入年資" prompt="請輸入 0 到 50 之間的整數（完整年數）" sqref="E3:E7" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>0</formula1>
-      <formula2>50</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="日期錯誤" error="到職日期必須介於 1990/1/1 至今日之間" promptTitle="輸入到職日期" prompt="請輸入格式為 YYYY/MM/DD 的到職日期（1990/1/1 至今）" sqref="F3:F7" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>DATE(1990,1,1)</formula1>
-      <formula2>TODAY()</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="輸入錯誤" error="請從下拉選單選擇有效的部門名稱" promptTitle="選擇部門" prompt="請從清單中選擇員工所屬部門" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>C3:C7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="輸入錯誤" error="請從下拉選單選擇有效的職級" promptTitle="選擇職級" prompt="請從清單中選擇員工職級" xr:uid="{00000000-0002-0000-0000-000001000000}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3:D7</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>